--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:49</t>
+    <t xml:space="preserve">2026-09-24 00:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -650,13 +650,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.42</v>
+        <v>0.03</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.26</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="8">
@@ -673,13 +673,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -696,13 +696,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="11">
@@ -742,13 +742,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="12">
@@ -765,13 +765,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.29</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="13">
@@ -788,13 +788,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.43</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="14">
@@ -814,7 +814,7 @@
         <v>0.76</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.94</v>
@@ -857,13 +857,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.12</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="17">
@@ -880,13 +880,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="18">
@@ -1017,13 +1017,13 @@
         <v>16</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.25</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="25">
@@ -1040,13 +1040,13 @@
         <v>16</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -1063,13 +1063,13 @@
         <v>16</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="27">
@@ -1086,13 +1086,13 @@
         <v>16</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="28">
@@ -1109,13 +1109,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="29">
@@ -1132,13 +1132,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="30">
@@ -1155,13 +1155,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31">
@@ -1204,7 +1204,7 @@
         <v>-0.44</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>-0.43</v>
@@ -1224,13 +1224,13 @@
         <v>16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>-0.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="34">
@@ -1247,13 +1247,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>-0.21</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="35">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:40</t>
+    <t xml:space="preserve">2026-10-01 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:14</t>
+    <t xml:space="preserve">2026-10-05 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
